--- a/delta/dist/20261025_台達電模型_v0.2.xlsx
+++ b/delta/dist/20261025_台達電模型_v0.2.xlsx
@@ -5892,7 +5892,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6129,7 +6129,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6250,7 +6250,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6371,7 +6371,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6492,7 +6492,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6613,7 +6613,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
